--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_4_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_4_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319229.1376669946</v>
+        <v>303580.0039790322</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547408</v>
+        <v>3013503.893776012</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20373567.1449482</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813755.887318159</v>
+        <v>4790382.659738132</v>
       </c>
     </row>
     <row r="11">
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>12.91010078545518</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1253,19 +1253,19 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1293,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>19.82224313344406</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>12.91010078545518</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1560,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2741920426674135</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1639,19 +1639,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9608114308426601</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1685,13 +1685,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1806,13 +1806,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>22.54368386855027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1840,19 +1840,19 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -1958,25 +1958,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>22.02246762618612</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2071,16 +2071,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2113,22 +2113,22 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>94.38361247260485</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2153,16 +2153,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>140.0190651869245</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>52.20357801874876</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2195,22 +2195,22 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2229,55 +2229,55 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2308,19 +2308,19 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.252730413754638</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2350,13 +2350,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="24">
@@ -2432,13 +2432,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>63.88882306452221</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
@@ -2447,7 +2447,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>4.525096818297269</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>50.46697834767983</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2590,19 +2590,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>21.15688084962317</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2621,31 +2621,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>83.08101808495465</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>17.57153846140836</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2684,13 +2684,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2827,28 +2827,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.252730413754582</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,31 +2858,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0276159785541</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2912,22 +2912,22 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>150.9993436124999</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3016,16 +3016,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>220.2131257424249</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>179.3813007854552</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3079,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>50.05769526855308</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3143,28 +3143,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>31.77750887508272</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -3174,61 +3174,61 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>112.3289263072337</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -3301,19 +3301,19 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>215</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="36">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3353,10 +3353,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>74.29715711450335</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -3392,16 +3392,16 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>116.325098768111</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3453,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>44.30348359856706</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3493,10 +3493,10 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>9.234466016111838</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3535,31 +3535,31 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3584,10 +3584,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>110.1805830381299</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3620,19 +3620,19 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>35.40726547353833</v>
       </c>
       <c r="T39" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3693,13 +3693,13 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S40" t="n">
-        <v>130.4655268502615</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3727,19 +3727,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>177.6197007854553</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>177.9933921796108</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3824,10 +3824,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3857,25 +3857,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>88.21022706868195</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>106.238736956606</v>
       </c>
     </row>
     <row r="43">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>74.62772033681219</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>48.36509407418593</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>22.10246781155966</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>22.10246781155966</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.3000000000003</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348996</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>92.93786803496215</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>66.67524177233588</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>40.41261550970962</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55.43434343434343</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C17" t="n">
-        <v>55.43434343434343</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D17" t="n">
-        <v>55.43434343434343</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E17" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L17" t="n">
-        <v>57.68</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M17" t="n">
-        <v>85.40000000000001</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N17" t="n">
-        <v>112</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V17" t="n">
-        <v>83.71717171717171</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W17" t="n">
-        <v>83.71717171717171</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X17" t="n">
-        <v>55.43434343434343</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y17" t="n">
-        <v>55.43434343434343</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L18" t="n">
-        <v>57.68</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>85.40000000000001</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N18" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>55.43434343434343</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>27.15151515151514</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="V18" t="n">
-        <v>2.24</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="X18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="S19" t="n">
-        <v>109.3334016426122</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="T19" t="n">
-        <v>109.3334016426122</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="U19" t="n">
-        <v>87.08848484848485</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="V19" t="n">
-        <v>58.80565656565657</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="W19" t="n">
-        <v>58.80565656565657</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="X19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="C20" t="n">
-        <v>262.7143434343434</v>
+        <v>710.516763498309</v>
       </c>
       <c r="D20" t="n">
-        <v>262.7143434343434</v>
+        <v>467.067986854209</v>
       </c>
       <c r="E20" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>812.6170525846973</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S20" t="n">
-        <v>601.4856691642474</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T20" t="n">
-        <v>601.4856691642474</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U20" t="n">
-        <v>506.1486868686869</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V20" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W20" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X20" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y20" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424092</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>445.9787825692111</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="C21" t="n">
-        <v>445.9787825692111</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="D21" t="n">
-        <v>445.9787825692111</v>
+        <v>377.7840429764083</v>
       </c>
       <c r="E21" t="n">
-        <v>304.5453833904995</v>
+        <v>218.5465879709528</v>
       </c>
       <c r="F21" t="n">
-        <v>158.0108254173845</v>
+        <v>72.01202999783774</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>248.2299999999999</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M21" t="n">
-        <v>486.8199999999999</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N21" t="n">
-        <v>725.41</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O21" t="n">
-        <v>964</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>689.4131260035546</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U21" t="n">
-        <v>689.4131260035546</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V21" t="n">
-        <v>689.4131260035546</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="W21" t="n">
-        <v>445.9787825692111</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="X21" t="n">
-        <v>445.9787825692111</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="Y21" t="n">
-        <v>445.9787825692111</v>
+        <v>526.7184526376595</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>752.8686165795501</v>
+        <v>710.516763498309</v>
       </c>
       <c r="C23" t="n">
-        <v>752.8686165795501</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D23" t="n">
-        <v>752.8686165795501</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E23" t="n">
-        <v>509.4342731452067</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F23" t="n">
-        <v>265.9999297108633</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>22.56558627651984</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>22.56558627651984</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>22.56558627651984</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S23" t="n">
-        <v>752.8686165795501</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T23" t="n">
-        <v>752.8686165795501</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U23" t="n">
-        <v>752.8686165795501</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V23" t="n">
-        <v>752.8686165795501</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W23" t="n">
-        <v>752.8686165795501</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X23" t="n">
-        <v>752.8686165795501</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y23" t="n">
-        <v>752.8686165795501</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>19.28</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M24" t="n">
-        <v>257.87</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N24" t="n">
-        <v>496.46</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O24" t="n">
-        <v>735.0500000000001</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>689.4131260035546</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T24" t="n">
-        <v>487.2265313623206</v>
+        <v>726.1056462496665</v>
       </c>
       <c r="U24" t="n">
-        <v>259.0029130987097</v>
+        <v>497.8820279860555</v>
       </c>
       <c r="V24" t="n">
-        <v>23.85080486696694</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.28</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="C26" t="n">
-        <v>19.28</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>942.6294132832089</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S26" t="n">
-        <v>731.498029862759</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="T26" t="n">
-        <v>506.1486868686869</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="U26" t="n">
-        <v>262.7143434343434</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="V26" t="n">
-        <v>19.28</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="W26" t="n">
-        <v>19.28</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="X26" t="n">
-        <v>19.28</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="Y26" t="n">
-        <v>19.28</v>
+        <v>569.2254314512334</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>193.733029281127</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="C27" t="n">
-        <v>19.28</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M27" t="n">
-        <v>304.1765223866491</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N27" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U27" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V27" t="n">
-        <v>728.8478917682573</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="W27" t="n">
-        <v>485.4135483339139</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="X27" t="n">
-        <v>485.4135483339139</v>
+        <v>526.7184526376595</v>
       </c>
       <c r="Y27" t="n">
-        <v>277.65324956896</v>
+        <v>526.7184526376595</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>960.7144137234802</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U29" t="n">
-        <v>749.5830303030303</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V29" t="n">
-        <v>749.5830303030303</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W29" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X29" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>567.561044716321</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="C30" t="n">
-        <v>567.561044716321</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D30" t="n">
-        <v>418.6266350550698</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E30" t="n">
-        <v>418.6266350550698</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F30" t="n">
-        <v>272.1340936625909</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G30" t="n">
-        <v>133.4032682452064</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H30" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>144.6375600578374</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M30" t="n">
-        <v>304.1765223866491</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U30" t="n">
-        <v>735.7763817363891</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V30" t="n">
-        <v>735.7763817363891</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W30" t="n">
-        <v>735.7763817363891</v>
+        <v>609.3459713618265</v>
       </c>
       <c r="X30" t="n">
-        <v>735.7763817363891</v>
+        <v>401.4944711562937</v>
       </c>
       <c r="Y30" t="n">
-        <v>735.7763817363891</v>
+        <v>193.7341723913397</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.2</v>
+        <v>485.167420504237</v>
       </c>
       <c r="C32" t="n">
-        <v>17.2</v>
+        <v>485.167420504237</v>
       </c>
       <c r="D32" t="n">
-        <v>17.2</v>
+        <v>241.7186438601369</v>
       </c>
       <c r="E32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>504.9505276501126</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>710.8050498573519</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>860</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T32" t="n">
-        <v>668.7151515151515</v>
+        <v>728.6161971483371</v>
       </c>
       <c r="U32" t="n">
-        <v>668.7151515151515</v>
+        <v>728.6161971483371</v>
       </c>
       <c r="V32" t="n">
-        <v>668.7151515151515</v>
+        <v>728.6161971483371</v>
       </c>
       <c r="W32" t="n">
-        <v>451.5434343434343</v>
+        <v>728.6161971483371</v>
       </c>
       <c r="X32" t="n">
-        <v>234.3717171717172</v>
+        <v>728.6161971483371</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.2</v>
+        <v>728.6161971483371</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.95413265278571</v>
+        <v>69.84447166430675</v>
       </c>
       <c r="C33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M33" t="n">
-        <v>230.05</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N33" t="n">
-        <v>442.9</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O33" t="n">
-        <v>655.75</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P33" t="n">
-        <v>838.3934776133508</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>827.9015061867851</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>654.484161637454</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T33" t="n">
-        <v>452.2975669962201</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U33" t="n">
-        <v>235.1258498245029</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V33" t="n">
-        <v>235.1258498245029</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W33" t="n">
-        <v>17.95413265278571</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="X33" t="n">
-        <v>17.95413265278571</v>
+        <v>277.6047704292607</v>
       </c>
       <c r="Y33" t="n">
-        <v>17.95413265278571</v>
+        <v>69.84447166430675</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>234.3717171717172</v>
+        <v>132.7447050367114</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>504.9505276501126</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>710.8050498573519</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>860</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>860</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S35" t="n">
-        <v>860</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T35" t="n">
-        <v>642.8282828282828</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="U35" t="n">
-        <v>451.5434343434343</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="V35" t="n">
-        <v>234.3717171717172</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="W35" t="n">
-        <v>234.3717171717172</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="X35" t="n">
-        <v>234.3717171717172</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="Y35" t="n">
-        <v>234.3717171717172</v>
+        <v>132.7447050367114</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>252.2392211072345</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C36" t="n">
-        <v>252.2392211072345</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D36" t="n">
-        <v>252.2392211072345</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E36" t="n">
-        <v>93.001766101779</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F36" t="n">
-        <v>93.001766101779</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G36" t="n">
-        <v>93.001766101779</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H36" t="n">
-        <v>93.001766101779</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I36" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>142.5575600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>355.4075600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M36" t="n">
-        <v>568.2575600578374</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N36" t="n">
-        <v>647.15</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O36" t="n">
-        <v>860</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>686.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>686.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U36" t="n">
-        <v>686.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V36" t="n">
-        <v>469.4109382789517</v>
+        <v>846.5570557448675</v>
       </c>
       <c r="W36" t="n">
-        <v>252.2392211072345</v>
+        <v>603.1082791007675</v>
       </c>
       <c r="X36" t="n">
-        <v>252.2392211072345</v>
+        <v>395.2567788952347</v>
       </c>
       <c r="Y36" t="n">
-        <v>252.2392211072345</v>
+        <v>187.4964801302808</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>961.308225475175</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>874.2758585542716</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y37" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>451.5434343434343</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="C38" t="n">
-        <v>234.3717171717172</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="D38" t="n">
-        <v>17.2</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="E38" t="n">
-        <v>17.2</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="F38" t="n">
-        <v>17.2</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R38" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S38" t="n">
-        <v>849.9083846317729</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T38" t="n">
-        <v>849.9083846317729</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U38" t="n">
-        <v>849.9083846317729</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="V38" t="n">
-        <v>849.9083846317729</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="W38" t="n">
-        <v>668.7151515151515</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="X38" t="n">
-        <v>668.7151515151515</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="Y38" t="n">
-        <v>451.5434343434343</v>
+        <v>284.1276524520142</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>267.2243436377178</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C39" t="n">
-        <v>267.2243436377178</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D39" t="n">
-        <v>267.2243436377178</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E39" t="n">
-        <v>267.2243436377178</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F39" t="n">
-        <v>267.2243436377178</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>128.4935182203333</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>142.5575600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>355.4075600578374</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>568.2575600578374</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="N39" t="n">
-        <v>781.1075600578374</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O39" t="n">
-        <v>790.6054414866707</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>686.5826554506689</v>
+        <v>928.2922408909005</v>
       </c>
       <c r="T39" t="n">
-        <v>484.3960608094349</v>
+        <v>726.1056462496665</v>
       </c>
       <c r="U39" t="n">
-        <v>267.2243436377178</v>
+        <v>497.8820279860555</v>
       </c>
       <c r="V39" t="n">
-        <v>267.2243436377178</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W39" t="n">
-        <v>267.2243436377178</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X39" t="n">
-        <v>267.2243436377178</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y39" t="n">
-        <v>267.2243436377178</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>148.9833604548096</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q40" t="n">
-        <v>148.9833604548096</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R40" t="n">
-        <v>148.9833604548096</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>196.4538391772275</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="C41" t="n">
-        <v>17.04</v>
+        <v>628.0253748412023</v>
       </c>
       <c r="D41" t="n">
-        <v>17.04</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>17.04</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>197.1158515846586</v>
+        <v>300.1647985849684</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>511.4548195661379</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="T41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="U41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="V41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="W41" t="n">
-        <v>626.7568694802578</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="X41" t="n">
-        <v>626.7568694802578</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="Y41" t="n">
-        <v>411.6053543287427</v>
+        <v>843.6054391011446</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>130.4091355924207</v>
+        <v>107.3735702322309</v>
       </c>
       <c r="C42" t="n">
-        <v>130.4091355924207</v>
+        <v>107.3735702322309</v>
       </c>
       <c r="D42" t="n">
-        <v>130.4091355924207</v>
+        <v>107.3735702322309</v>
       </c>
       <c r="E42" t="n">
-        <v>130.4091355924207</v>
+        <v>107.3735702322309</v>
       </c>
       <c r="F42" t="n">
-        <v>130.4091355924207</v>
+        <v>107.3735702322309</v>
       </c>
       <c r="G42" t="n">
-        <v>130.4091355924207</v>
+        <v>107.3735702322309</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>107.3735702322309</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>390.368997361522</v>
       </c>
       <c r="N42" t="n">
-        <v>775.0075600578374</v>
+        <v>390.368997361522</v>
       </c>
       <c r="O42" t="n">
-        <v>775.0075600578374</v>
+        <v>601.6590183426915</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>762.8987605366849</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>560.712165895451</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U42" t="n">
-        <v>345.5606507439359</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V42" t="n">
-        <v>130.4091355924207</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W42" t="n">
-        <v>130.4091355924207</v>
+        <v>422.536925949487</v>
       </c>
       <c r="X42" t="n">
-        <v>130.4091355924207</v>
+        <v>214.6854257439542</v>
       </c>
       <c r="Y42" t="n">
-        <v>130.4091355924207</v>
+        <v>107.3735702322309</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="V43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="W43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="X43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Y43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
     </row>
     <row r="44">
@@ -8439,16 +8439,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,19 +8512,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>156.2912070328283</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
         <v>133.9744074143302</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652335</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8670,19 +8670,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>255.0477063711817</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
         <v>231.2329957552695</v>
@@ -8758,16 +8758,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>158.9239023638252</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8907,13 +8907,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
@@ -8922,7 +8922,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>256.1824907047645</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,16 +8986,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>156.2912070328283</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
         <v>142.5962444444444</v>
@@ -9068,16 +9068,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
         <v>135.0065633140411</v>
@@ -9144,19 +9144,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>258.3462332272727</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
-        <v>256.2817504652778</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O17" t="n">
-        <v>230.0982114216867</v>
+        <v>256.5734881866366</v>
       </c>
       <c r="P17" t="n">
         <v>231.2329957552695</v>
@@ -9223,19 +9223,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>165.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L18" t="n">
-        <v>166.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>170.1340339220183</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N18" t="n">
-        <v>158.2103989520202</v>
+        <v>157.8169888482831</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
         <v>133.9744074143302</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9396,7 +9396,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9463,22 +9463,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>369.8170060425004</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>295.1552315763977</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9700,22 +9700,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>197.6503338623806</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
-        <v>295.1415200271288</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>303.2845009208181</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>349.0484638974528</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10171,22 +10171,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>303.2845009208181</v>
+        <v>382.1386950879875</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
         <v>139.9817740860215</v>
@@ -10335,7 +10335,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>437.0731727773048</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10414,19 +10414,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>161.806544173546</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>437.0731727773048</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10581,7 +10581,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>211.031045358245</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>360.302996258564</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10809,7 +10809,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>346.5074603610917</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10882,22 +10882,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>357.7767872515269</v>
       </c>
       <c r="O39" t="n">
-        <v>152.1900640695285</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
         <v>210.0772877358491</v>
@@ -11040,16 +11040,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>220.0898510449805</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>442.643829968084</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
-        <v>437.3469244119842</v>
+        <v>333.8446085143028</v>
       </c>
       <c r="O41" t="n">
         <v>380.8001812627454</v>
@@ -11122,19 +11122,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>179.1516856726523</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
-        <v>141.6490351202224</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
         <v>210.0772877358491</v>
@@ -23023,16 +23023,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>196.1099688007902</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
         <v>251.3456529078365</v>
@@ -23044,10 +23044,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>343.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>360.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -23111,19 +23111,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>174.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>199.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>225.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
-        <v>182.8721852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
         <v>205.6826957773044</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>141.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>2.447248692438784</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,7 +23178,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
         <v>86.16204325169439</v>
@@ -23227,7 +23227,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
         <v>415.302737515135</v>
@@ -23236,7 +23236,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23260,13 +23260,13 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>136.9590171556945</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
         <v>223.0958495641314</v>
@@ -23294,10 +23294,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>140.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>146.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D12" t="n">
         <v>147.4450655646388</v>
@@ -23354,7 +23354,7 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>209.8997871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
         <v>251.6949831609196</v>
@@ -23363,7 +23363,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
-        <v>179.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="13">
@@ -23400,7 +23400,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,16 +23418,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>227.6713973856141</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23476,7 +23476,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23497,19 +23497,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>148.908306510307</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>225.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23543,13 +23543,13 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.1684123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -23585,7 +23585,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
-        <v>174.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
         <v>225.9413820809748</v>
@@ -23664,13 +23664,13 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T16" t="n">
-        <v>201.9455894282815</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U16" t="n">
-        <v>260.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V16" t="n">
-        <v>226.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W16" t="n">
         <v>286.522998336591</v>
@@ -23679,7 +23679,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y16" t="n">
-        <v>196.0409694835445</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="17">
@@ -23698,19 +23698,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E17" t="n">
-        <v>357.2679700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>378.8760457417114</v>
+        <v>382.574751492425</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -23749,13 +23749,13 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
-        <v>299.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W17" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X17" t="n">
-        <v>341.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y17" t="n">
         <v>386.2379386560536</v>
@@ -23816,25 +23816,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>72.15783415264313</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>143.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>172.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>201.2789820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>251.6949831609196</v>
+        <v>227.3936889116331</v>
       </c>
       <c r="X18" t="n">
-        <v>205.7729852034775</v>
+        <v>178.1829599431613</v>
       </c>
       <c r="Y18" t="n">
         <v>205.6826957773044</v>
@@ -23865,10 +23865,10 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H19" t="n">
-        <v>134.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I19" t="n">
-        <v>127.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J19" t="n">
         <v>93.35918011667277</v>
@@ -23892,7 +23892,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.16204325169439</v>
+        <v>63.71328389118497</v>
       </c>
       <c r="R19" t="n">
         <v>177.2933913771695</v>
@@ -23904,16 +23904,16 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>264.2965617303047</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>224.137643323828</v>
+        <v>224.5476180635119</v>
       </c>
       <c r="W19" t="n">
-        <v>286.522998336591</v>
+        <v>258.9329730762748</v>
       </c>
       <c r="X19" t="n">
-        <v>225.7096553890372</v>
+        <v>198.119630128721</v>
       </c>
       <c r="Y19" t="n">
         <v>218.5846533520948</v>
@@ -23929,16 +23929,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D20" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E20" t="n">
-        <v>381.9303700722618</v>
+        <v>179.6356836433646</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
         <v>415.302737515135</v>
@@ -23971,22 +23971,22 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>156.9620404352316</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
         <v>349.240968717413</v>
@@ -24011,16 +24011,16 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>17.62601526847644</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>85.13993914446186</v>
       </c>
       <c r="H21" t="n">
         <v>112.2354442364965</v>
@@ -24053,22 +24053,22 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
@@ -24087,7 +24087,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>34.05985351325981</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
@@ -24135,7 +24135,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T22" t="n">
         <v>227.9455894282815</v>
@@ -24166,19 +24166,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>365.2728917710076</v>
+        <v>162.9782053421103</v>
       </c>
       <c r="D23" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24187,7 +24187,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>8.69655894085788</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24208,13 +24208,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
         <v>223.0958495641314</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="24">
@@ -24290,13 +24290,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>136.2759056302994</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -24305,7 +24305,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>247.1698863426223</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
@@ -24336,7 +24336,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24390,7 +24390,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="26">
@@ -24400,13 +24400,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>382.7338416634806</v>
+        <v>332.2668633158007</v>
       </c>
       <c r="C26" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D26" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E26" t="n">
         <v>381.9303700722618</v>
@@ -24424,7 +24424,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24448,19 +24448,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>128.7122370915265</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24479,31 +24479,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>83.45216556491268</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>140.0735419939926</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24533,7 +24533,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
@@ -24542,13 +24542,13 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -24609,7 +24609,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T28" t="n">
         <v>227.9455894282815</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24643,7 +24643,7 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
@@ -24685,28 +24685,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>146.6163875273951</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,31 +24716,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04159641482979737</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24770,22 +24770,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>100.6956395484197</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24846,7 +24846,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S31" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T31" t="n">
         <v>227.9455894282815</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="32">
@@ -24874,16 +24874,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C32" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E32" t="n">
-        <v>381.9303700722618</v>
+        <v>161.7172443298368</v>
       </c>
       <c r="F32" t="n">
         <v>406.8760457417114</v>
@@ -24928,7 +24928,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>43.71454877867617</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
@@ -24937,13 +24937,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>134.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>154.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24956,7 +24956,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>122.6508037197626</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
@@ -24977,7 +24977,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,28 +25001,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>68.38032527756042</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>36.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25032,7 +25032,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>46.64501259656925</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C34" t="n">
         <v>167.2468210986278</v>
@@ -25086,7 +25086,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
-        <v>227.9455894282815</v>
+        <v>94.7586218429135</v>
       </c>
       <c r="U34" t="n">
         <v>286.3190293564909</v>
@@ -25114,7 +25114,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>252.9439654637738</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25123,7 +25123,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
         <v>415.302737515135</v>
@@ -25159,19 +25159,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>8.095849564131356</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>61.97365290783654</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>112.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
@@ -25180,7 +25180,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="36">
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>172.7084989883157</v>
@@ -25199,7 +25199,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
@@ -25211,10 +25211,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>15.09947573691173</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25241,7 +25241,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
@@ -25250,16 +25250,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>116.4754883813142</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25275,7 +25275,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D37" t="n">
-        <v>15.4285054328443</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E37" t="n">
         <v>146.4339626465692</v>
@@ -25311,13 +25311,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786024</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25351,10 +25351,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>150.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D38" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
         <v>381.9303700722618</v>
@@ -25369,10 +25369,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>210.4758895704059</v>
+        <v>201.2414235542941</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25393,31 +25393,31 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>169.8596679319578</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25442,10 +25442,10 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>2.054861198366524</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
         <v>89.39663285141508</v>
@@ -25478,19 +25478,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>136.2759056302995</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
@@ -25551,13 +25551,13 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S40" t="n">
-        <v>93.55107118671071</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
         <v>227.9455894282815</v>
@@ -25585,19 +25585,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>187.6531909855523</v>
+        <v>151.8486281536646</v>
       </c>
       <c r="D41" t="n">
-        <v>354.683041620683</v>
+        <v>176.6896494410722</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>168.5061064549189</v>
       </c>
       <c r="F41" t="n">
-        <v>406.8760457417114</v>
+        <v>193.4517821243685</v>
       </c>
       <c r="G41" t="n">
         <v>415.302737515135</v>
@@ -25648,13 +25648,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>136.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>173.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="42">
@@ -25682,10 +25682,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0.7465913262578567</v>
@@ -25715,25 +25715,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>83.47294403515588</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>12.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>19.80058714942527</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>99.44395882069837</v>
       </c>
     </row>
     <row r="43">
@@ -25743,7 +25743,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>46.64501259656925</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C43" t="n">
         <v>167.2468210986278</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350379.9730845937</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350379.9730845937</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350379.9730845935</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352026.7318511438</v>
+        <v>351700.8745024338</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>507017.9003687725</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>507017.9003687725</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>507017.9003687725</v>
+        <v>507028.2310008515</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>507017.9003687723</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488220.3124503887</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488220.3124503887</v>
+        <v>507028.2310008515</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488220.3124503888</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486774.3441489746</v>
+        <v>487081.0800200352</v>
       </c>
     </row>
     <row r="16">
@@ -26264,46 +26264,46 @@
         <v>69879.81359544017</v>
       </c>
       <c r="C2" t="n">
+        <v>69879.81359544015</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69879.81359544014</v>
+      </c>
+      <c r="E2" t="n">
         <v>69879.81359544017</v>
       </c>
-      <c r="D2" t="n">
-        <v>74664.77104961485</v>
-      </c>
-      <c r="E2" t="n">
-        <v>74664.77104961485</v>
-      </c>
       <c r="F2" t="n">
-        <v>74664.77104961486</v>
+        <v>69879.81359544017</v>
       </c>
       <c r="G2" t="n">
-        <v>75015.25300292441</v>
+        <v>74945.90033124232</v>
       </c>
       <c r="H2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="I2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="J2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="K2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="L2" t="n">
-        <v>104001.521742606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="M2" t="n">
-        <v>104001.521742606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="N2" t="n">
-        <v>104001.5217426061</v>
+        <v>108004.437145366</v>
       </c>
       <c r="O2" t="n">
-        <v>103693.774302606</v>
+        <v>103759.0573236672</v>
       </c>
       <c r="P2" t="n">
-        <v>69879.81359544017</v>
+        <v>69879.81359544014</v>
       </c>
     </row>
     <row r="3">
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>7562.01207347375</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="C4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="D4" t="n">
-        <v>23026.20207384747</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="E4" t="n">
-        <v>23026.20207384747</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="F4" t="n">
-        <v>23026.20207384747</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="G4" t="n">
-        <v>23137.88272891696</v>
+        <v>24752.61367588639</v>
       </c>
       <c r="H4" t="n">
-        <v>33649.14617662695</v>
+        <v>36022.33037502109</v>
       </c>
       <c r="I4" t="n">
-        <v>33649.14617662695</v>
+        <v>36022.3303750211</v>
       </c>
       <c r="J4" t="n">
-        <v>33649.14617662695</v>
+        <v>36022.33037502109</v>
       </c>
       <c r="K4" t="n">
-        <v>33649.14617662695</v>
+        <v>36022.33037502109</v>
       </c>
       <c r="L4" t="n">
-        <v>32374.32258066736</v>
+        <v>36022.33037502109</v>
       </c>
       <c r="M4" t="n">
-        <v>32374.32258066736</v>
+        <v>36022.33037502109</v>
       </c>
       <c r="N4" t="n">
-        <v>32374.32258066736</v>
+        <v>36022.33037502109</v>
       </c>
       <c r="O4" t="n">
-        <v>32276.259227132</v>
+        <v>34575.07249607201</v>
       </c>
       <c r="P4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>13226.6383122918</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>13226.63831229178</v>
       </c>
       <c r="D6" t="n">
-        <v>8353.788975767369</v>
+        <v>13226.63831229177</v>
       </c>
       <c r="E6" t="n">
-        <v>50057.76897576737</v>
+        <v>46854.2383122918</v>
       </c>
       <c r="F6" t="n">
-        <v>50057.76897576739</v>
+        <v>46854.2383122918</v>
       </c>
       <c r="G6" t="n">
-        <v>49626.80027400745</v>
+        <v>40953.80104605495</v>
       </c>
       <c r="H6" t="n">
-        <v>2230.975285979057</v>
+        <v>-255.3491357483872</v>
       </c>
       <c r="I6" t="n">
-        <v>59700.29228597904</v>
+        <v>57328.43800658325</v>
       </c>
       <c r="J6" t="n">
-        <v>59700.29228597909</v>
+        <v>57328.4380065833</v>
       </c>
       <c r="K6" t="n">
-        <v>59700.29228597907</v>
+        <v>57328.43800658325</v>
       </c>
       <c r="L6" t="n">
-        <v>58555.19916193868</v>
+        <v>57328.43800658331</v>
       </c>
       <c r="M6" t="n">
-        <v>58555.19916193865</v>
+        <v>57328.43800658328</v>
       </c>
       <c r="N6" t="n">
-        <v>58555.1991619387</v>
+        <v>57328.43800658327</v>
       </c>
       <c r="O6" t="n">
-        <v>58467.11507547402</v>
+        <v>56207.78959966078</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915088</v>
+        <v>46854.23831229177</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,19 +26895,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26916,25 +26916,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35094,16 +35094,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,19 +35167,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26.00000000000029</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,19 +35325,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35413,16 +35413,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,13 +35562,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -35577,7 +35577,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,16 +35641,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -35723,16 +35723,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -35799,19 +35799,19 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
-        <v>26.86868686868686</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -35878,19 +35878,19 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N18" t="n">
-        <v>26.86868686868686</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36051,7 +36051,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36118,22 +36118,22 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>231.2626262626262</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>161.1808241620674</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36355,22 +36355,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
-        <v>161.1671126127986</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>161.1504669987997</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36756,7 +36756,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N29" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O29" t="n">
         <v>150.7019698410586</v>
@@ -36826,22 +36826,22 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>161.1504669987997</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -36990,7 +36990,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>206.726939550032</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37069,19 +37069,19 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>21.82477008752445</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37227,7 +37227,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>206.726939550032</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37236,7 +37236,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>79.6893332749117</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37464,7 +37464,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>116.1612271338189</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37537,22 +37537,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="O39" t="n">
-        <v>9.59381962508408</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
         <v>70.09551364982758</v>
@@ -37695,16 +37695,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>212.2975967408112</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
-        <v>207.9338608153932</v>
+        <v>104.4315449177119</v>
       </c>
       <c r="O41" t="n">
         <v>150.7019698410586</v>
@@ -37777,19 +37777,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>37.01765175063403</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
-        <v>7.674627705892183</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
         <v>70.09551364982758</v>
